--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\download\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B98F405-E61A-4272-9A49-802EE7DA39C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4920" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Codebook" sheetId="1" r:id="rId5"/>
+    <sheet name="Codebook" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -26,10 +35,6 @@
 (timestamp)</t>
   </si>
   <si>
-    <t>Submission time as text: YYYY/MM/DD h:mm:ss, with AM or PM, GMT-4.
-Blank: missing submission time.</t>
-  </si>
-  <si>
     <t>Course-specific Student ID
 (studentID)</t>
   </si>
@@ -79,17 +84,6 @@
   <si>
     <t>Activities during Study Breaks
 (break_activities)</t>
-  </si>
-  <si>
-    <t>Social: socializing or interacting with other people.
-Eating: eating food.
-Napping: taking a nap.
-Gaming: playing games.
-Exercise: physical exercise.
-Space Out: zoning out or taking unfocused rest.
-None: no reported break activity.
-Rotting on instagram specifically: retained write-in about Instagram use.
-Multiple labels are separated by '; '; all reported selections are retained. Blank: missing response.</t>
   </si>
   <si>
     <t>Total Weekly Study Time (hours)
@@ -116,17 +110,6 @@
   <si>
     <t>Prior Statistics Course Grade (approximate percentage)
 (prior_grade_pct)</t>
-  </si>
-  <si>
-    <t>-1: Prefer not say
-55: 50%-59% (D- to D+)
-65: 60%-69% (C- to C+).
-75: 70%-79% (B- to B+).
-85: 80%-89% (A- to A).
-95: 90%-100% (A+).
-Approximate representatives of the grade bands in the current data, rather than exact individual grades.
-Courses: STA258H5, STA260H5, STA238H1, STA255H1 or ECO227Y5; average if multiple were taken.
-Blank: Prefer not to say.</t>
   </si>
   <si>
     <t>Agreement that Breaks Improve Study Efficiency (numeric code)
@@ -148,6 +131,24 @@
 (study_location)</t>
   </si>
   <si>
+    <t>Data Quality and Preparation Notes
+(data_notes)</t>
+  </si>
+  <si>
+    <t>Imputed: numeric substitute for a textual interval or lower-bound response.
+OUTLIER: weekly study time above 168 hours.
+Unmapped year: unrecognized year response.
+Prefer not to say / unmapped: no usable grade code.
+Missing studentID: ID not provided.
+Invalid studentID (URL detected): a URL entered in the ID field.
+Notes are separated by semicolons. Blank: no note recorded; this does not prove all values are valid. These notes are not thematic-analysis codes.</t>
+  </si>
+  <si>
+    <t>Submission time as text: YYYY/MM/DD h:mm:ss, GMT-4.
+Blank: missing submission time.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Home/home: at home. Library/library: in a library.
 Cafe: in a cafe.
 Lecture hall(but self-study in lecture hall): self-study in a lecture hall.
@@ -155,49 +156,74 @@
 Outdoors(park, beach, etc): outdoors.
 UTM buildings like IB or MN / University Buildings (e.g. MN): campus-building write-ins.
 gfuih: uninterpretable write-in.
-Multiple labels are separated by '; '. Case variants, write-ins and all reported selections are retained. Blank: missing response.</t>
-  </si>
-  <si>
-    <t>Data Quality and Preparation Notes
-(data_notes)</t>
-  </si>
-  <si>
-    <t>Imputed: numeric substitute for a textual interval or lower-bound response.
-OUTLIER: weekly study time above 168 hours.
-Unmapped year: unrecognized year response.
-Prefer not to say / unmapped: no usable grade code.
-Missing studentID: ID not provided.
-Invalid studentID (URL detected): a URL entered in the ID field.
-Notes are separated by semicolons. Blank: no note recorded; this does not prove all values are valid. These notes are not thematic-analysis codes.</t>
+Multiple labels are separated by ', '. Case variants, write-ins and all reported selections are retained. Blank: missing response.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Social: socializing or interacting with other people.
+Eating: eating food.
+Napping: taking a nap.
+Gaming: playing games.
+Exercise: physical exercise.
+Space Out: zoning out or taking unfocused rest.
+None: no reported break activity.
+Rotting on instagram specifically: retained write-in about Instagram use.
+Multiple labels are separated by ', '; all reported selections are retained. Blank: missing response.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(space): Prefer not say
+55: 50%-59% (D- to D+)
+65: 60%-69% (C- to C+).
+75: 70%-79% (B- to B+).
+85: 80%-89% (A- to A).
+95: 90%-100% (A+).
+Approximate representatives of the grade bands in the current data, rather than exact individual grades.
+Courses: STA258H5, STA260H5, STA238H1, STA255H1 or ECO227Y5; average if multiple were taken.
+Blank: Prefer not to say.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -205,7 +231,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -215,7 +241,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -229,45 +261,48 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -457,31 +492,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="53.38"/>
-    <col customWidth="1" min="2" max="2" width="133.0"/>
+    <col min="1" max="1" width="53.42578125" customWidth="1"/>
+    <col min="2" max="2" width="133" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -489,111 +527,112 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B98F405-E61A-4272-9A49-802EE7DA39C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCDE851-BF12-48F2-9F43-894770FB0BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Codebook" sheetId="1" r:id="rId1"/>
@@ -112,6 +112,17 @@
 (prior_grade_pct)</t>
   </si>
   <si>
+    <t>-1: Prefer not say
+55: 50%-59% (D- to D+)
+65: 60%-69% (C- to C+).
+75: 70%-79% (B- to B+).
+85: 80%-89% (A- to A).
+95: 90%-100% (A+).
+Approximate representatives of the grade bands in the current data, rather than exact individual grades.
+Courses: STA258H5, STA260H5, STA238H1, STA255H1 or ECO227Y5; average if multiple were taken.
+Blank: Prefer not to say.</t>
+  </si>
+  <si>
     <t>Agreement that Breaks Improve Study Efficiency (numeric code)
 (break_helps_efficiency)</t>
   </si>
@@ -169,18 +180,6 @@
 None: no reported break activity.
 Rotting on instagram specifically: retained write-in about Instagram use.
 Multiple labels are separated by ', '; all reported selections are retained. Blank: missing response.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>(space): Prefer not say
-55: 50%-59% (D- to D+)
-65: 60%-69% (C- to C+).
-75: 70%-79% (B- to B+).
-85: 80%-89% (A- to A).
-95: 90%-100% (A+).
-Approximate representatives of the grade bands in the current data, rather than exact individual grades.
-Courses: STA258H5, STA260H5, STA238H1, STA255H1 or ECO227Y5; average if multiple were taken.
-Blank: Prefer not to say.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -532,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -580,7 +579,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -603,32 +602,32 @@
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>28</v>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="1" r:id="R3bed7456b7b2446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="1" r:id="Ra0042b25144b4a75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -582,7 +582,7 @@
 Blank: missing or unrecognized response.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="190" customHeight="1">
+    <x:row r="13" ht="240" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
@@ -593,6 +593,7 @@
 75 = 70%-79% (B- to B+)
 85 = 80%-89% (A- to A)
 95 = 90%-100% (A+).
+Below 50% = questionnaire option; no corresponding record is identifiable in the current dataset. No numeric code has been assigned for this category.
 Courses: STA258H5, STA260H5, STA238H1, STA255H1 or ECO227Y5; the supplied questionnaire asks for the average if multiple were taken. Existing numeric codes are unchanged.
 Four whitespace-only entries were standardized to blank. The source does not distinguish their reasons for missingness. No -1 code occurs in this dataset.
 Blank: unavailable grade; do not infer a specific reason.</x:v>
